--- a/server-side/modelling/results/hossain svm tables.xlsx
+++ b/server-side/modelling/results/hossain svm tables.xlsx
@@ -25,6 +25,8 @@
     <sheet name="hossain svm 100 0p01 metrics" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="hossain svm 100 0p001 cm" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="hossain svm 100 0p001 metrics" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="hossain svm 1000 0p001 cm" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="hossain svm 1000 0p001 metrics" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2871,6 +2873,232 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>true_negative</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>false_positive</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>false_negative</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>true_positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5867</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1288</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3973</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11257</v>
+      </c>
+      <c r="C3" t="n">
+        <v>113</v>
+      </c>
+      <c r="D3" t="n">
+        <v>901</v>
+      </c>
+      <c r="E3" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12377</v>
+      </c>
+      <c r="C4" t="n">
+        <v>51</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E4" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11588</v>
+      </c>
+      <c r="C5" t="n">
+        <v>67</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1091</v>
+      </c>
+      <c r="E5" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12476</v>
+      </c>
+      <c r="C6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D6" t="n">
+        <v>678</v>
+      </c>
+      <c r="E6" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11302</v>
+      </c>
+      <c r="C7" t="n">
+        <v>19</v>
+      </c>
+      <c r="D7" t="n">
+        <v>514</v>
+      </c>
+      <c r="E7" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9799</v>
+      </c>
+      <c r="C8" t="n">
+        <v>111</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1209</v>
+      </c>
+      <c r="E8" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14219</v>
+      </c>
+      <c r="C9" t="n">
+        <v>106</v>
+      </c>
+      <c r="D9" t="n">
+        <v>780</v>
+      </c>
+      <c r="E9" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11050</v>
+      </c>
+      <c r="C10" t="n">
+        <v>58</v>
+      </c>
+      <c r="D10" t="n">
+        <v>676</v>
+      </c>
+      <c r="E10" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>12384</v>
+      </c>
+      <c r="C11" t="n">
+        <v>329</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E11" t="n">
+        <v>569</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3125,6 +3353,267 @@
       </c>
       <c r="F11" t="n">
         <v>0.8969014478561936</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>prec</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>rec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.7854406130268199</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.7851438407218401</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8551387394825409</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7849742265109693</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7854406130268199</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9206013624618276</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9063981704428501</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8449876548790065</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9137998117365602</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9206013624618276</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9191570599897202</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8915207323095613</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7110326766811595</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9054088453528146</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9191570599897202</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9118385991625428</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8903781490388049</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7843113963384233</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9070922575036326</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9118385991625428</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.946251027883681</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9311108296642004</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8073944087204192</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9399503971485317</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.946251027883681</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9552927361181009</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.940120272387024</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.758778798284107</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9496566224186427</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9552927361181009</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8895767107244437</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8721997619564632</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8501688632131452</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8888871827890457</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8895767107244437</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9421482206986614</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9278850077974418</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7650505403070849</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9296742885467957</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9421482206986614</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9390567917635337</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9248643964440044</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8315985206627086</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9326561369416049</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9390567917635337</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.9059942645310205</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8942379748443531</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8411428351794512</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8920498144340636</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9059942645310205</v>
       </c>
     </row>
   </sheetData>
